--- a/docs/eip/dependency-licence-inventory.xlsx
+++ b/docs/eip/dependency-licence-inventory.xlsx
@@ -84,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +154,11 @@
         <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -189,7 +194,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -312,6 +317,9 @@
       <alignment horizontal="general" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1060,7 +1068,7 @@
     <row r="18" ht="15" customHeight="1" s="21">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>2. Replace the Redis image with Valkey (BSD-3-Clause) or pin redis:7.2; keep RedisInsight out of customer builds.</t>
+          <t>2. ✅ Redis image replaced by Valkey 9.1.2 (BSD-3-Clause) on 07/10; keep RedisInsight out of customer builds.</t>
         </is>
       </c>
     </row>
@@ -62480,42 +62488,42 @@
     <row r="7" ht="46.25" customHeight="1" s="21">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>Redis</t>
+          <t>Valkey</t>
         </is>
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
-          <t>redis:7 (floats to 7.4.x)</t>
+          <t>valkey/valkey:9.1.2</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>Cache</t>
+          <t>Cache (Compose service redis)</t>
         </is>
       </c>
       <c r="D7" s="25" t="inlineStr">
         <is>
-          <t>Separate container</t>
+          <t>Separate container, unmodified</t>
         </is>
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>RSALv2 or SSPLv1 (Redis 7.4+). 7.2 and earlier: BSD-3-Clause</t>
-        </is>
-      </c>
-      <c r="F7" s="38" t="inlineStr">
-        <is>
-          <t>Source-available</t>
-        </is>
-      </c>
-      <c r="G7" s="38" t="inlineStr">
-        <is>
-          <t>Replace (recommended)</t>
+          <t>BSD-3-Clause</t>
+        </is>
+      </c>
+      <c r="F7" s="42" t="inlineStr">
+        <is>
+          <t>Permissive</t>
+        </is>
+      </c>
+      <c r="G7" s="42" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>RSALv2 lets us use Redis inside Horus (it forbids offering Redis itself as a service). But it is not open source, enterprise legal reviews flag it, and a floating tag can change licence silently. Switch to Valkey (valkey/valkey, BSD-3-Clause, Redis-compatible – redis-py works unchanged) or pin redis:7.2.</t>
+          <t>Keep notice. Replaced redis:7 (Redis 7.4, RSALv2 or SSPLv1) on 07/10/2026; same protocol, redis-py unchanged.</t>
         </is>
       </c>
     </row>
@@ -63721,9 +63729,9 @@
       <c r="A3" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="40" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="B3" s="41" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C3" s="25" t="inlineStr">
@@ -63748,7 +63756,7 @@
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>Switch to Valkey (BSD-3-Clause, drop-in, redis-py unchanged) or pin redis:7.2.</t>
+          <t>Replaced by valkey/valkey:9.1.2 (BSD-3-Clause); service name and REDIS_* settings unchanged.</t>
         </is>
       </c>
       <c r="H3" s="31" t="inlineStr">
@@ -63758,7 +63766,7 @@
       </c>
       <c r="I3" s="31" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done (07/10)</t>
         </is>
       </c>
     </row>

--- a/docs/eip/dependency-licence-inventory.xlsx
+++ b/docs/eip/dependency-licence-inventory.xlsx
@@ -1068,7 +1068,7 @@
     <row r="18" ht="15" customHeight="1" s="21">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>2. ✅ Redis image replaced by Valkey 9.1.2 (BSD-3-Clause) on 07/10; keep RedisInsight out of customer builds.</t>
+          <t>2. ✅ Redis image replaced by Valkey 9.1.2 (BSD-3-Clause) on 07/10; RedisInsight and pgAdmin only in the dev-tools profile, which the installer never starts.</t>
         </is>
       </c>
     </row>
@@ -62540,7 +62540,7 @@
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>DB admin UI (admin profile)</t>
+          <t>DB admin UI (dev-tools profile)</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
@@ -62565,7 +62565,7 @@
       </c>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>Licence OK. Keep it out of the customer profile anyway (admin UI with default credentials).</t>
+          <t>Licence OK. Development tool only: Compose profile dev-tools, which the installer never starts (admin UI with default credentials).</t>
         </is>
       </c>
     </row>
@@ -62582,7 +62582,7 @@
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>Cache admin UI (admin profile)</t>
+          <t>Cache admin UI (dev-tools profile)</t>
         </is>
       </c>
       <c r="D9" s="25" t="inlineStr">
@@ -62607,7 +62607,7 @@
       </c>
       <c r="H9" s="25" t="inlineStr">
         <is>
-          <t>Team/debug tool only. Exclude from the customer bundle.</t>
+          <t>Team/debug tool only: Compose profile dev-tools, which the installer never starts, so it is not in a customer install.</t>
         </is>
       </c>
     </row>
@@ -63774,9 +63774,9 @@
       <c r="A4" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="40" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
@@ -63786,7 +63786,7 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>src/infra/docker-compose.yml (admin profile)</t>
+          <t>src/infra/docker-compose.yml (dev-tools profile)</t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
@@ -63801,7 +63801,7 @@
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>Exclude from the customer bundle; keep for the team only.</t>
+          <t>RedisInsight and pgAdmin moved to the Compose profile dev-tools; the installer never starts it and no longer checks their ports.</t>
         </is>
       </c>
       <c r="H4" s="31" t="inlineStr">
@@ -63811,7 +63811,7 @@
       </c>
       <c r="I4" s="31" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done (07/10)</t>
         </is>
       </c>
     </row>

--- a/docs/eip/dependency-licence-inventory.xlsx
+++ b/docs/eip/dependency-licence-inventory.xlsx
@@ -775,7 +775,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="21">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -790,7 +789,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="23.85" customHeight="1" s="21">
       <c r="A7" s="26" t="inlineStr">
         <is>
@@ -1050,7 +1048,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="21">
       <c r="A16" s="24" t="inlineStr">
         <is>
@@ -1093,7 +1090,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="21">
       <c r="A23" s="24" t="inlineStr">
         <is>
@@ -62451,7 +62447,7 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>postgres:latest</t>
+          <t>postgres:18.6</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
@@ -62481,7 +62477,7 @@
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t>Pin a major version instead of latest.</t>
+          <t>Pinned to 18.6, the version latest gave on 07/10/2026.</t>
         </is>
       </c>
     </row>
@@ -62535,7 +62531,7 @@
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>dpage/pgadmin4:latest</t>
+          <t>dpage/pgadmin4:9.18.0</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
@@ -62577,7 +62573,7 @@
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>redis/redisinsight:latest</t>
+          <t>redis/redisinsight:3.8.0</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
@@ -62745,7 +62741,7 @@
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>prom/prometheus:latest</t>
+          <t>prom/prometheus:v3.15.0</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
@@ -62775,7 +62771,7 @@
       </c>
       <c r="H13" s="25" t="inlineStr">
         <is>
-          <t>Pin a version instead of latest.</t>
+          <t>Pinned to v3.15.0, the version latest gave on 07/10/2026.</t>
         </is>
       </c>
     </row>
@@ -62787,7 +62783,7 @@
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>python:3.11-slim (Debian)</t>
+          <t>python:3.11.17-slim (Debian)</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
@@ -62829,7 +62825,7 @@
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>node:20-alpine</t>
+          <t>node:20.20.2-alpine</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">

--- a/docs/eip/dependency-licence-inventory.xlsx
+++ b/docs/eip/dependency-licence-inventory.xlsx
@@ -775,6 +775,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="21">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -789,6 +790,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="23.85" customHeight="1" s="21">
       <c r="A7" s="26" t="inlineStr">
         <is>
@@ -1048,6 +1050,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="21">
       <c r="A16" s="24" t="inlineStr">
         <is>
@@ -1079,7 +1082,7 @@
     <row r="20" ht="15" customHeight="1" s="21">
       <c r="A20" s="29" t="inlineStr">
         <is>
-          <t>4. Pin versions + add a CI licence gate (fail on AGPL/GPL/SSPL inside our processes).</t>
+          <t>4. ✅ Lock files with hashes, pinned image tags and the CI licence gate (job licences, 07/10).</t>
         </is>
       </c>
     </row>
@@ -1090,6 +1093,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="21">
       <c r="A23" s="24" t="inlineStr">
         <is>
@@ -63860,9 +63864,9 @@
       <c r="A6" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
@@ -63887,7 +63891,7 @@
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>Pin versions (uv pip compile → lock files), pin image tags, and add a CI licence gate that fails on AGPL/GPL/SSPL inside our processes.</t>
+          <t>requirements*.lock with hashes for every service, every image tag pinned, and the CI job licences: THIRD_PARTY_NOTICES --check, and it fails on GPL/AGPL/SSPL in our own processes (exceptions in scripts/licences/allowlist.yaml).</t>
         </is>
       </c>
       <c r="H6" s="31" t="inlineStr">
@@ -63897,7 +63901,7 @@
       </c>
       <c r="I6" s="31" t="inlineStr">
         <is>
-          <t>To do</t>
+          <t>Done (07/10)</t>
         </is>
       </c>
     </row>

--- a/docs/eip/dependency-licence-inventory.xlsx
+++ b/docs/eip/dependency-licence-inventory.xlsx
@@ -771,11 +771,10 @@
     <row r="2" ht="15" customHeight="1" s="21">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>Snapshot 24/09/2026, updated 07/10/2026 · prepared for ADR-004 (closed-source licence)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Snapshot 24/09/2026, updated 08/10/2026 · prepared for ADR-004 (closed-source licence)</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="15" customHeight="1" s="21">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -790,7 +789,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="23.85" customHeight="1" s="21">
       <c r="A7" s="26" t="inlineStr">
         <is>
@@ -1050,7 +1048,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="21">
       <c r="A16" s="24" t="inlineStr">
         <is>
@@ -1093,7 +1090,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="21">
       <c r="A23" s="24" t="inlineStr">
         <is>
@@ -62817,7 +62813,7 @@
       </c>
       <c r="H14" s="25" t="inlineStr">
         <is>
-          <t>Normal OS aggregation.</t>
+          <t>Normal OS aggregation. Its GPL and LGPL packages are listed, with the written offer for their source, in THIRD_PARTY_NOTICES section 7 (08/10).</t>
         </is>
       </c>
     </row>
@@ -62859,7 +62855,7 @@
       </c>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>Normal OS aggregation.</t>
+          <t>Normal OS aggregation. Its GPL and LGPL packages are listed, with the written offer for their source, in THIRD_PARTY_NOTICES section 7 (08/10).</t>
         </is>
       </c>
     </row>
@@ -62901,7 +62897,7 @@
       </c>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>Separate program = aggregation, Horus code unaffected. Ship the GPL text + source offer, or replace pdf2image+poppler with pypdfium2 (already installed, Apache-2.0/BSD).</t>
+          <t>Separate program = aggregation, Horus code unaffected. GPL texts in LICENSES/, written offer in THIRD_PARTY_NOTICES section 7, sources gathered by scripts/licences/fetch-gpl-sources.py (08/10). Replacing pdf2image+poppler with pypdfium2 would also remove GnuPG, which poppler pulls in.</t>
         </is>
       </c>
     </row>
@@ -62955,17 +62951,17 @@
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>Debian packages in mas image</t>
+          <t>Debian packages in the mas builder stage</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>Compilers left in the final image</t>
+          <t>Compilers of the build stage, not shipped</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>Build tools (single-stage Dockerfile)</t>
+          <t>Build tools (builder stage of a multi-stage Dockerfile)</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
@@ -62978,14 +62974,14 @@
           <t>Strong copyleft</t>
         </is>
       </c>
-      <c r="G18" s="33" t="inlineStr">
-        <is>
-          <t>OK – conditions</t>
+      <c r="G18" s="42" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="H18" s="25" t="inlineStr">
         <is>
-          <t>Runtime-library exception covers compiled output. Better: multi-stage build so compilers are not shipped (smaller, fewer licences to declare).</t>
+          <t>Not in the image since 08/10: the MAS Dockerfile is multi-stage and its final stage installs no system package.</t>
         </is>
       </c>
     </row>
@@ -63954,9 +63950,9 @@
       <c r="A8" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
@@ -63981,7 +63977,7 @@
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>Keep as separate process + notice, or replace pdf2image with pypdfium2 rendering (removes GPL from the image).</t>
+          <t>Kept as a separate process. GPL texts in LICENSES/, written offer in THIRD_PARTY_NOTICES section 7, sources gathered by scripts/licences/fetch-gpl-sources.py. Replacing pdf2image with pypdfium2 rendering would remove it.</t>
         </is>
       </c>
       <c r="H8" s="31" t="inlineStr">
@@ -63991,7 +63987,7 @@
       </c>
       <c r="I8" s="31" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Done (08/10)</t>
         </is>
       </c>
     </row>
@@ -64179,9 +64175,9 @@
       <c r="A13" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
@@ -64206,7 +64202,7 @@
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>Move to requirements-dev.txt.</t>
+          <t>Moved to requirements-test.txt in each service, which only CI installs; no lock file names a test tool.</t>
         </is>
       </c>
       <c r="H13" s="31" t="inlineStr">
@@ -64216,7 +64212,7 @@
       </c>
       <c r="I13" s="31" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Done (08/10)</t>
         </is>
       </c>
     </row>

--- a/docs/eip/dependency-licence-inventory.xlsx
+++ b/docs/eip/dependency-licence-inventory.xlsx
@@ -62694,12 +62694,12 @@
     <row r="12" ht="23.85" customHeight="1" s="21">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>Promtail</t>
+          <t>Grafana Alloy</t>
         </is>
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>grafana/promtail:3.4.2</t>
+          <t>grafana/alloy:v1.20.1</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
@@ -62709,12 +62709,12 @@
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>Separate container</t>
+          <t>Separate container, reads the Docker socket read-only</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t>Apache-2.0 (Loki clients/ folder)</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="F12" s="32" t="inlineStr">
@@ -62729,7 +62729,7 @@
       </c>
       <c r="H12" s="25" t="inlineStr">
         <is>
-          <t>Licence OK, but Promtail reached end of life in March 2026 – migrate to Grafana Alloy (Apache-2.0).</t>
+          <t>Replaced Promtail (end of life since March 2026) on 08/10/2026, with the same Loki labels for /admin/logs. Pinned to v1.20.1.</t>
         </is>
       </c>
     </row>
@@ -64130,9 +64130,9 @@
       <c r="A12" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="32" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
@@ -64157,7 +64157,7 @@
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>Migrate to Grafana Alloy (Apache-2.0).</t>
+          <t>Replaced by grafana/alloy:v1.20.1 (Apache-2.0) with the same labels, so /admin/logs is unchanged. Row kept as a record.</t>
         </is>
       </c>
       <c r="H12" s="31" t="inlineStr">
@@ -64167,7 +64167,7 @@
       </c>
       <c r="I12" s="31" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Done (08/10)</t>
         </is>
       </c>
     </row>

--- a/docs/eip/dependency-licence-inventory.xlsx
+++ b/docs/eip/dependency-licence-inventory.xlsx
@@ -525,8 +525,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Services" displayName="Services" ref="A1:H18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Services" displayName="Services" ref="A1:H17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H17"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Component"/>
     <tableColumn id="2" name="Image / package"/>
@@ -775,6 +775,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="21">
       <c r="A4" s="24" t="inlineStr">
         <is>
@@ -789,6 +790,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="23.85" customHeight="1" s="21">
       <c r="A7" s="26" t="inlineStr">
         <is>
@@ -943,23 +945,23 @@
         </is>
       </c>
       <c r="B11" s="27">
-        <f>COUNTIF('Services &amp; images'!$F$2:$F$18,"Permissive")</f>
+        <f>COUNTIF('Services &amp; images'!$F$2:$F$17,"Permissive")</f>
         <v/>
       </c>
       <c r="C11" s="27">
-        <f>COUNTIF('Services &amp; images'!$F$2:$F$18,"Weak copyleft")</f>
+        <f>COUNTIF('Services &amp; images'!$F$2:$F$17,"Weak copyleft")</f>
         <v/>
       </c>
       <c r="D11" s="27">
-        <f>COUNTIF('Services &amp; images'!$F$2:$F$18,"Strong copyleft")</f>
+        <f>COUNTIF('Services &amp; images'!$F$2:$F$17,"Strong copyleft")</f>
         <v/>
       </c>
       <c r="E11" s="27">
-        <f>COUNTIF('Services &amp; images'!$F$2:$F$18,"Source-available")</f>
+        <f>COUNTIF('Services &amp; images'!$F$2:$F$17,"Source-available")</f>
         <v/>
       </c>
       <c r="F11" s="27">
-        <f>COUNTIF('Services &amp; images'!$F$2:$F$18,"Third-party proprietary")</f>
+        <f>COUNTIF('Services &amp; images'!$F$2:$F$17,"Third-party proprietary")</f>
         <v/>
       </c>
       <c r="G11" s="28">
@@ -967,7 +969,7 @@
         <v/>
       </c>
       <c r="H11" s="28">
-        <f>COUNTIF('Services &amp; images'!$G$2:$G$18,"Blocker*")</f>
+        <f>COUNTIF('Services &amp; images'!$G$2:$G$17,"Blocker*")</f>
         <v/>
       </c>
     </row>
@@ -1048,6 +1050,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="21">
       <c r="A16" s="24" t="inlineStr">
         <is>
@@ -1065,7 +1068,7 @@
     <row r="18" ht="15" customHeight="1" s="21">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>2. ✅ Redis image replaced by Valkey 9.1.2 (BSD-3-Clause) on 07/10; RedisInsight and pgAdmin only in the dev-tools profile, which the installer never starts.</t>
+          <t>2. ✅ Redis image replaced by Valkey 9.1.2 (BSD-3-Clause) on 07/10; RedisInsight (SSPL) removed on 08/10; pgAdmin only in the dev-tools profile, which the installer never starts.</t>
         </is>
       </c>
     </row>
@@ -1090,6 +1093,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="21">
       <c r="A23" s="24" t="inlineStr">
         <is>
@@ -62216,7 +62220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18" customWidth="1" style="20" min="1" max="1"/>
@@ -62565,67 +62569,67 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="21">
+    <row r="9" ht="35.05" customHeight="1" s="21">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>RedisInsight</t>
+          <t>Grafana Loki</t>
         </is>
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>redis/redisinsight:3.8.0</t>
+          <t>grafana/loki:3.4.2</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>Cache admin UI (dev-tools profile)</t>
+          <t>Log storage (/admin/logs)</t>
         </is>
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
-          <t>Separate container</t>
+          <t>Separate container, unmodified, HTTP API only</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
         <is>
-          <t>SSPL-1.0</t>
+          <t>AGPL-3.0-only</t>
         </is>
       </c>
       <c r="F9" s="38" t="inlineStr">
         <is>
-          <t>Source-available</t>
-        </is>
-      </c>
-      <c r="G9" s="38" t="inlineStr">
-        <is>
-          <t>Do not ship to customers</t>
+          <t>Strong copyleft</t>
+        </is>
+      </c>
+      <c r="G9" s="33" t="inlineStr">
+        <is>
+          <t>OK – conditions</t>
         </is>
       </c>
       <c r="H9" s="25" t="inlineStr">
         <is>
-          <t>Team/debug tool only: Compose profile dev-tools, which the installer never starts, so it is not in a customer install.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="35.05" customHeight="1" s="21">
+          <t>Does not make Horus AGPL: it is a separate program we talk to over HTTP. Conditions: never modify or fork it; ship the AGPL text + link to the exact upstream source. If a customer's policy bans AGPL, swap for an Apache-licensed store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="23.85" customHeight="1" s="21">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>Grafana Loki</t>
+          <t>Grafana Tempo</t>
         </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>grafana/loki:3.4.2</t>
+          <t>grafana/tempo:2.6.0</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>Log storage (/admin/logs)</t>
+          <t>Traces (/admin/traces)</t>
         </is>
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>Separate container, unmodified, HTTP API only</t>
+          <t>Separate container, unmodified, HTTP/OTLP</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
@@ -62645,71 +62649,71 @@
       </c>
       <c r="H10" s="25" t="inlineStr">
         <is>
-          <t>Does not make Horus AGPL: it is a separate program we talk to over HTTP. Conditions: never modify or fork it; ship the AGPL text + link to the exact upstream source. If a customer's policy bans AGPL, swap for an Apache-licensed store.</t>
+          <t>Same as Loki. Alternative if needed: Jaeger (Apache-2.0).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="23.85" customHeight="1" s="21">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>Grafana Tempo</t>
+          <t>Grafana Alloy</t>
         </is>
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>grafana/tempo:2.6.0</t>
+          <t>grafana/alloy:v1.20.1</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>Traces (/admin/traces)</t>
+          <t>Ships container logs to Loki</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>Separate container, unmodified, HTTP/OTLP</t>
+          <t>Separate container, reads the Docker socket read-only</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>AGPL-3.0-only</t>
-        </is>
-      </c>
-      <c r="F11" s="38" t="inlineStr">
-        <is>
-          <t>Strong copyleft</t>
-        </is>
-      </c>
-      <c r="G11" s="33" t="inlineStr">
-        <is>
-          <t>OK – conditions</t>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>Permissive</t>
+        </is>
+      </c>
+      <c r="G11" s="32" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="H11" s="25" t="inlineStr">
         <is>
-          <t>Same as Loki. Alternative if needed: Jaeger (Apache-2.0).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="23.85" customHeight="1" s="21">
+          <t>Replaced Promtail (end of life since March 2026) on 08/10/2026, with the same Loki labels for /admin/logs. Pinned to v1.20.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="21">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>Grafana Alloy</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>grafana/alloy:v1.20.1</t>
+          <t>prom/prometheus:v3.15.0</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>Ships container logs to Loki</t>
+          <t>Metrics (/admin/metrics)</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>Separate container, reads the Docker socket read-only</t>
+          <t>Separate container</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
@@ -62729,34 +62733,34 @@
       </c>
       <c r="H12" s="25" t="inlineStr">
         <is>
-          <t>Replaced Promtail (end of life since March 2026) on 08/10/2026, with the same Loki labels for /admin/logs. Pinned to v1.20.1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="21">
+          <t>Pinned to v3.15.0, the version latest gave on 07/10/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="23.85" customHeight="1" s="21">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>Python base image</t>
         </is>
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>prom/prometheus:v3.15.0</t>
+          <t>python:3.11.17-slim (Debian)</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>Metrics (/admin/metrics)</t>
+          <t>Base of mas, agent, knowledge-store</t>
         </is>
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>Separate container</t>
+          <t>OS layer</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>PSF-2.0 (Python) + Debian packages (mixed)</t>
         </is>
       </c>
       <c r="F13" s="32" t="inlineStr">
@@ -62771,24 +62775,24 @@
       </c>
       <c r="H13" s="25" t="inlineStr">
         <is>
-          <t>Pinned to v3.15.0, the version latest gave on 07/10/2026.</t>
+          <t>Normal OS aggregation. Its GPL and LGPL packages are listed, with the written offer for their source, in THIRD_PARTY_NOTICES section 7 (08/10).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="23.85" customHeight="1" s="21">
       <c r="A14" s="31" t="inlineStr">
         <is>
-          <t>Python base image</t>
+          <t>Node base image</t>
         </is>
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>python:3.11.17-slim (Debian)</t>
+          <t>node:20.20.2-alpine</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>Base of mas, agent, knowledge-store</t>
+          <t>Base of web-client</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
@@ -62798,7 +62802,7 @@
       </c>
       <c r="E14" s="25" t="inlineStr">
         <is>
-          <t>PSF-2.0 (Python) + Debian packages (mixed)</t>
+          <t>MIT (Node.js) + Alpine packages (mixed)</t>
         </is>
       </c>
       <c r="F14" s="32" t="inlineStr">
@@ -62820,49 +62824,49 @@
     <row r="15" ht="23.85" customHeight="1" s="21">
       <c r="A15" s="31" t="inlineStr">
         <is>
-          <t>Node base image</t>
+          <t>poppler-utils</t>
         </is>
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>node:20.20.2-alpine</t>
+          <t>Debian package in knowledge-store image</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>Base of web-client</t>
+          <t>PDF → image (called by pdf2image)</t>
         </is>
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>OS layer</t>
+          <t>Separate program (pdftoppm), not linked</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t>MIT (Node.js) + Alpine packages (mixed)</t>
-        </is>
-      </c>
-      <c r="F15" s="32" t="inlineStr">
-        <is>
-          <t>Permissive</t>
-        </is>
-      </c>
-      <c r="G15" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>GPL-2.0 or GPL-3.0</t>
+        </is>
+      </c>
+      <c r="F15" s="38" t="inlineStr">
+        <is>
+          <t>Strong copyleft</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="inlineStr">
+        <is>
+          <t>OK – conditions</t>
         </is>
       </c>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>Normal OS aggregation. Its GPL and LGPL packages are listed, with the written offer for their source, in THIRD_PARTY_NOTICES section 7 (08/10).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="23.85" customHeight="1" s="21">
+          <t>Separate program = aggregation, Horus code unaffected. GPL texts in LICENSES/, written offer in THIRD_PARTY_NOTICES section 7, sources gathered by scripts/licences/fetch-gpl-sources.py (08/10). Replacing pdf2image+poppler with pypdfium2 would also remove GnuPG, which poppler pulls in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="21">
       <c r="A16" s="31" t="inlineStr">
         <is>
-          <t>poppler-utils</t>
+          <t>tesseract-ocr</t>
         </is>
       </c>
       <c r="B16" s="31" t="inlineStr">
@@ -62872,119 +62876,78 @@
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>PDF → image (called by pdf2image)</t>
+          <t>OCR</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>Separate program (pdftoppm), not linked</t>
+          <t>Separate program via pytesseract</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t>GPL-2.0 or GPL-3.0</t>
-        </is>
-      </c>
-      <c r="F16" s="38" t="inlineStr">
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>Permissive</t>
+        </is>
+      </c>
+      <c r="G16" s="32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>Keep notice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="23.85" customHeight="1" s="21">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>build-essential / g++</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>Debian packages in the mas builder stage</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>Compilers of the build stage, not shipped</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>Build tools (builder stage of a multi-stage Dockerfile)</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>GPL-3.0 with GCC Runtime Library Exception</t>
+        </is>
+      </c>
+      <c r="F17" s="38" t="inlineStr">
         <is>
           <t>Strong copyleft</t>
         </is>
       </c>
-      <c r="G16" s="33" t="inlineStr">
-        <is>
-          <t>OK – conditions</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="inlineStr">
-        <is>
-          <t>Separate program = aggregation, Horus code unaffected. GPL texts in LICENSES/, written offer in THIRD_PARTY_NOTICES section 7, sources gathered by scripts/licences/fetch-gpl-sources.py (08/10). Replacing pdf2image+poppler with pypdfium2 would also remove GnuPG, which poppler pulls in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="21">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>tesseract-ocr</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr">
-        <is>
-          <t>Debian package in knowledge-store image</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>OCR</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>Separate program via pytesseract</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
-        <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>Permissive</t>
-        </is>
-      </c>
-      <c r="G17" s="32" t="inlineStr">
+      <c r="G17" s="42" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="H17" s="25" t="inlineStr">
         <is>
-          <t>Keep notice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="23.85" customHeight="1" s="21">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>build-essential / g++</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>Debian packages in the mas builder stage</t>
-        </is>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>Compilers of the build stage, not shipped</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>Build tools (builder stage of a multi-stage Dockerfile)</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>GPL-3.0 with GCC Runtime Library Exception</t>
-        </is>
-      </c>
-      <c r="F18" s="38" t="inlineStr">
-        <is>
-          <t>Strong copyleft</t>
-        </is>
-      </c>
-      <c r="G18" s="42" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="inlineStr">
-        <is>
           <t>Not in the image since 08/10: the MAS Dockerfile is multi-stage and its final stage installs no system package.</t>
         </is>
       </c>
     </row>
+    <row r="18" s="21"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -63782,7 +63745,7 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>src/infra/docker-compose.yml (dev-tools profile)</t>
+          <t>src/infra/docker-compose.yml</t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
@@ -63797,7 +63760,7 @@
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>RedisInsight and pgAdmin moved to the Compose profile dev-tools; the installer never starts it and no longer checks their ports.</t>
+          <t>Removed from the Compose file on 08/10 (its connection was never set up); valkey-cli in the redis container does the same job. pgAdmin stays in the dev-tools profile.</t>
         </is>
       </c>
       <c r="H4" s="31" t="inlineStr">
@@ -63807,7 +63770,7 @@
       </c>
       <c r="I4" s="31" t="inlineStr">
         <is>
-          <t>Done (07/10)</t>
+          <t>Done (08/10)</t>
         </is>
       </c>
     </row>
